--- a/Expérience/Calcul phi0.xlsx
+++ b/Expérience/Calcul phi0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pacom\Documents\Cours\2025-2026\TIPE_Spé\Expérience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318D3656-416B-4527-9455-FE36822E0F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0843D8-81AB-49CE-90BF-28053A11DAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0A9082E9-4009-4283-B142-A09E54A10779}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>V_mot</t>
   </si>
@@ -53,10 +53,67 @@
     <t>Oméga (rad/s)</t>
   </si>
   <si>
-    <t>Couple (N/m)</t>
-  </si>
-  <si>
     <t>r</t>
+  </si>
+  <si>
+    <t>Couple (Nm)</t>
+  </si>
+  <si>
+    <t>Vmax</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>10V</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>V6</t>
+  </si>
+  <si>
+    <t>V7</t>
+  </si>
+  <si>
+    <t>15V</t>
+  </si>
+  <si>
+    <t>V8</t>
+  </si>
+  <si>
+    <t>0.056 Ohm</t>
+  </si>
+  <si>
+    <t>1,05 ohm</t>
+  </si>
+  <si>
+    <t>V9</t>
+  </si>
+  <si>
+    <t>17V</t>
+  </si>
+  <si>
+    <t>V10</t>
+  </si>
+  <si>
+    <t>Trop proche</t>
+  </si>
+  <si>
+    <t>V11</t>
+  </si>
+  <si>
+    <t>V12</t>
   </si>
 </sst>
 </file>
@@ -318,7 +375,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="fr-FR"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -485,7 +542,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="fr-FR"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1339,16 +1396,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>10556</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>94817</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>353800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>172047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>700463</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>70569</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>279991</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>147798</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1693,13 +1750,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F23D01-6C8E-4716-B7A0-85D79D0825DB}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1716,15 +1773,24 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="O1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>950</v>
       </c>
       <c r="B2">
-        <f>A2*2*3.1415*(1/60)</f>
+        <f t="shared" ref="B2:B7" si="0">A2*2*3.1415*(1/60)</f>
         <v>99.480833333333337</v>
       </c>
       <c r="C2">
@@ -1740,13 +1806,26 @@
         <f>E2*0.001*0.06</f>
         <v>1.0319999999999999E-3</v>
       </c>
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2">
+        <v>15.6</v>
+      </c>
+      <c r="P2">
+        <v>210</v>
+      </c>
+      <c r="Q2">
+        <f>0.0661*P2*0.01</f>
+        <v>0.13881000000000002</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1380</v>
       </c>
       <c r="B3">
-        <f>A3*2*3.1415*(1/60)</f>
+        <f t="shared" si="0"/>
         <v>144.50900000000001</v>
       </c>
       <c r="C3">
@@ -1759,16 +1838,32 @@
         <v>26</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G7" si="0">E3*0.001*0.06</f>
+        <f t="shared" ref="G3:G7" si="1">E3*0.001*0.06</f>
         <v>1.56E-3</v>
       </c>
+      <c r="N3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3">
+        <v>12.8</v>
+      </c>
+      <c r="P3">
+        <v>200</v>
+      </c>
+      <c r="Q3">
+        <f>0.0661*P3*0.01</f>
+        <v>0.13220000000000001</v>
+      </c>
+      <c r="R3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1850</v>
       </c>
       <c r="B4">
-        <f>A4*2*3.1415*(1/60)</f>
+        <f t="shared" si="0"/>
         <v>193.72583333333336</v>
       </c>
       <c r="C4">
@@ -1781,16 +1876,32 @@
         <v>35.700000000000003</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.1420000000000002E-3</v>
       </c>
+      <c r="N4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4">
+        <v>14</v>
+      </c>
+      <c r="P4">
+        <v>180</v>
+      </c>
+      <c r="Q4">
+        <f>0.0661*P4*0.01</f>
+        <v>0.11898000000000002</v>
+      </c>
+      <c r="R4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2600</v>
       </c>
       <c r="B5">
-        <f>A5*2*3.1415*(1/60)</f>
+        <f t="shared" si="0"/>
         <v>272.26333333333332</v>
       </c>
       <c r="C5">
@@ -1803,16 +1914,32 @@
         <v>51</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0600000000000002E-3</v>
       </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5">
+        <v>11.4</v>
+      </c>
+      <c r="P5">
+        <v>450</v>
+      </c>
+      <c r="Q5">
+        <f>0.0661*P5*0.01</f>
+        <v>0.29744999999999999</v>
+      </c>
+      <c r="R5" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3045</v>
       </c>
       <c r="B6">
-        <f>A6*2*3.1415*(1/60)</f>
+        <f t="shared" si="0"/>
         <v>318.86225000000002</v>
       </c>
       <c r="C6">
@@ -1825,16 +1952,32 @@
         <v>60.3</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.6179999999999997E-3</v>
       </c>
+      <c r="N6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6">
+        <v>10.6</v>
+      </c>
+      <c r="P6">
+        <v>740</v>
+      </c>
+      <c r="Q6">
+        <f>0.0661*P6*0.01</f>
+        <v>0.48914000000000002</v>
+      </c>
+      <c r="R6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3440</v>
       </c>
       <c r="B7">
-        <f>A7*2*3.1415*(1/60)</f>
+        <f t="shared" si="0"/>
         <v>360.22533333333331</v>
       </c>
       <c r="C7">
@@ -1847,13 +1990,124 @@
         <v>68.8</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.1279999999999997E-3</v>
       </c>
+      <c r="N7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7">
+        <v>9.1</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="M8">
+        <f>0.4*0.06</f>
+        <v>2.4E-2</v>
+      </c>
+      <c r="N8" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8">
+        <v>9.1</v>
+      </c>
+      <c r="P8">
+        <v>140</v>
+      </c>
+      <c r="R8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="N9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="P9">
+        <v>620</v>
+      </c>
+      <c r="Q9">
+        <f>0.0661*P9*0.01</f>
+        <v>0.40982000000000007</v>
+      </c>
+      <c r="R9" t="s">
+        <v>20</v>
+      </c>
+      <c r="S9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="N10" t="s">
+        <v>16</v>
+      </c>
+      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10">
+        <v>350</v>
+      </c>
+      <c r="Q10">
+        <f>0.0661*P10*0.01</f>
+        <v>0.23135000000000003</v>
+      </c>
+      <c r="R10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="N11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
+      </c>
+      <c r="P11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K12" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12">
+        <v>9.6</v>
+      </c>
+      <c r="P12">
+        <v>725</v>
+      </c>
+      <c r="Q12">
+        <f>0.0661*P12*0.01</f>
+        <v>0.47922500000000007</v>
+      </c>
+      <c r="R12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="N13" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13">
+        <v>12.6</v>
+      </c>
+      <c r="P13">
+        <v>300</v>
+      </c>
+      <c r="Q13">
+        <f>0.0661*P13*0.01</f>
+        <v>0.19830000000000003</v>
+      </c>
+      <c r="R13" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
